--- a/excel/output_stats_vfvv/2mm/EfficiencyStats.xlsx
+++ b/excel/output_stats_vfvv/2mm/EfficiencyStats.xlsx
@@ -490,28 +490,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53.8296</v>
+        <v>53.9247</v>
       </c>
       <c r="D2" t="n">
-        <v>20.0354</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>44.643</v>
+        <v>44.7097</v>
       </c>
       <c r="F2" t="n">
         <v>357.41</v>
       </c>
       <c r="G2" t="n">
-        <v>357.24</v>
+        <v>359.84</v>
       </c>
       <c r="H2" t="n">
-        <v>344.422</v>
+        <v>342.391</v>
       </c>
       <c r="I2" t="n">
-        <v>343.393</v>
+        <v>341.179</v>
       </c>
       <c r="J2" t="n">
-        <v>21084100000</v>
+        <v>21102200000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
